--- a/site/Paycor-to-Entra-ID-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Paycor-to-Entra-ID-Event-Based-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,86 +617,394 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Integration Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01K0EPNYJEHDW4TQRTN6PXT579</t>
+          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01K0EPNYJEHDW4TQRTN6PXT579</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
+          <t>01KF2RH05MP5RR93W69VEMT2AR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#01KF2RH05MP5RR93W69VEMT2AR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>User Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KKGR0E1X4WS9VGW91EW6JMB7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01KKGR0E1X4WS9VGW91EW6JMB7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>01KF2ST6Y7GH70E2MJCYT5X2DZ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#01KF2ST6Y7GH70E2MJCYT5X2DZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>User Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KRG2661TDEHWCKHA9TA6VZHE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01KRG2661TDEHWCKHA9TA6VZHE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>User Process Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KRG2C2G6577BS6ZZHRQYW1HM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01KRG2C2G6577BS6ZZHRQYW1HM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sensitive Fields</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KKGR0E1X2J8YA1DX900C9W7D</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01KKGR0E1X2J8YA1DX900C9W7D</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notification Template Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Success Execution</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Failure Execution</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Event-Based-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
